--- a/data/2025/metadata/data_inventory.xlsx
+++ b/data/2025/metadata/data_inventory.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/drotto/src/jiflr/data/2025/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53DA5416-EEC2-8943-8E6A-D66EABF17990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D720A247-0A5F-1A41-9810-EC846048D1B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="880" windowWidth="34900" windowHeight="22500" activeTab="1" xr2:uid="{834A5152-98D4-1D4E-9988-BEC817907187}"/>
+    <workbookView xWindow="1180" yWindow="780" windowWidth="34820" windowHeight="22600" xr2:uid="{834A5152-98D4-1D4E-9988-BEC817907187}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="106">
   <si>
     <t>site_id</t>
   </si>
@@ -160,12 +160,6 @@
     <t>site_type</t>
   </si>
   <si>
-    <t>temperature</t>
-  </si>
-  <si>
-    <t>intensive</t>
-  </si>
-  <si>
     <t>There was a 0 cm sensor here that failed before being deployed</t>
   </si>
   <si>
@@ -178,9 +172,6 @@
     <t>Missing 0m data file</t>
   </si>
   <si>
-    <t>camp</t>
-  </si>
-  <si>
     <t>C17</t>
   </si>
   <si>
@@ -205,9 +196,6 @@
     <t>C8</t>
   </si>
   <si>
-    <t>other</t>
-  </si>
-  <si>
     <t>llewellyn_terminus</t>
   </si>
   <si>
@@ -332,6 +320,42 @@
   </si>
   <si>
     <t>"A02 200" written on sensor and bag. By photo geotag, G04 -&gt; G03 order, and jeremy sensors at 1m, this is not the site at the bottom of the C10 hill</t>
+  </si>
+  <si>
+    <t>on_ice_standard</t>
+  </si>
+  <si>
+    <t>on_ice_intensive</t>
+  </si>
+  <si>
+    <t>on_ice_camp</t>
+  </si>
+  <si>
+    <t>off_ice_standard</t>
+  </si>
+  <si>
+    <t>Venus Mine</t>
+  </si>
+  <si>
+    <t>AB Mountain</t>
+  </si>
+  <si>
+    <t>Carcross Hanger</t>
+  </si>
+  <si>
+    <t>Dail Peak</t>
+  </si>
+  <si>
+    <t>Fraser Wx</t>
+  </si>
+  <si>
+    <t>Klondike  Wx</t>
+  </si>
+  <si>
+    <t>Muffys House</t>
+  </si>
+  <si>
+    <t>Poole Point</t>
   </si>
 </sst>
 </file>
@@ -797,8 +821,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{30214729-FAD1-AB4C-91D6-A2D7E03E2CE5}" name="Table2" displayName="Table2" ref="A1:K47" totalsRowShown="0" headerRowDxfId="11" tableBorderDxfId="10">
-  <autoFilter ref="A1:K47" xr:uid="{30214729-FAD1-AB4C-91D6-A2D7E03E2CE5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{30214729-FAD1-AB4C-91D6-A2D7E03E2CE5}" name="Table2" displayName="Table2" ref="A1:K56" totalsRowShown="0" headerRowDxfId="11" tableBorderDxfId="10">
+  <autoFilter ref="A1:K56" xr:uid="{30214729-FAD1-AB4C-91D6-A2D7E03E2CE5}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{D1314852-2294-C84C-828A-C37A76432716}" name="site_type"/>
     <tableColumn id="2" xr3:uid="{57B08370-AE15-194A-9E89-74600FFA2010}" name="site_id" dataDxfId="9"/>
@@ -1133,7 +1157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{282355AC-F746-9947-AE42-F19047015063}">
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.83203125" customWidth="1"/>
@@ -1153,16 +1177,16 @@
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>34</v>
@@ -1182,7 +1206,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>1</v>
@@ -1210,12 +1234,12 @@
         <v>26</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>2</v>
@@ -1248,7 +1272,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>3</v>
@@ -1279,7 +1303,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>4</v>
@@ -1310,7 +1334,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>5</v>
@@ -1333,13 +1357,13 @@
       <c r="H6" s="11"/>
       <c r="I6" s="5"/>
       <c r="J6" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K6" s="8"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>6</v>
@@ -1368,7 +1392,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B8" s="17" t="s">
         <v>7</v>
@@ -1399,7 +1423,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>8</v>
@@ -1430,7 +1454,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>9</v>
@@ -1459,7 +1483,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>10</v>
@@ -1490,7 +1514,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>11</v>
@@ -1518,12 +1542,12 @@
         <v>26</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B13" s="17" t="s">
         <v>12</v>
@@ -1554,7 +1578,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>13</v>
@@ -1585,7 +1609,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>14</v>
@@ -1616,7 +1640,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B16" s="17" t="s">
         <v>15</v>
@@ -1647,7 +1671,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B17" s="17" t="s">
         <v>16</v>
@@ -1678,7 +1702,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B18" s="17" t="s">
         <v>17</v>
@@ -1709,7 +1733,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B19" s="17" t="s">
         <v>18</v>
@@ -1740,7 +1764,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B20" s="17" t="s">
         <v>19</v>
@@ -1771,7 +1795,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B21" s="17" t="s">
         <v>20</v>
@@ -1802,7 +1826,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B22" s="17" t="s">
         <v>21</v>
@@ -1833,7 +1857,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B23" s="17" t="s">
         <v>22</v>
@@ -1864,7 +1888,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B24" s="17" t="s">
         <v>28</v>
@@ -1895,7 +1919,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B25" s="17" t="s">
         <v>29</v>
@@ -1926,10 +1950,10 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>38</v>
@@ -1959,10 +1983,10 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>38</v>
@@ -1990,7 +2014,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B28" s="17" t="s">
         <v>30</v>
@@ -2047,10 +2071,10 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C31" s="8">
         <v>22038781</v>
@@ -2076,10 +2100,10 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C32" s="8">
         <v>22038779</v>
@@ -2107,10 +2131,10 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C33" s="8">
         <v>22038776</v>
@@ -2138,10 +2162,10 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C34" s="8">
         <v>22038777</v>
@@ -2169,10 +2193,10 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C35" s="8">
         <v>22038778</v>
@@ -2212,10 +2236,10 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="12"/>
@@ -2229,40 +2253,40 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D38" s="13"/>
       <c r="J38" s="15"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D39" s="13"/>
       <c r="J39" s="15"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
+        <v>96</v>
+      </c>
+      <c r="B40" t="s">
         <v>46</v>
-      </c>
-      <c r="B40" t="s">
-        <v>49</v>
       </c>
       <c r="D40" s="13"/>
       <c r="J40" s="15"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="14"/>
@@ -2276,57 +2300,237 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D42" s="13"/>
       <c r="J42" s="15"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="B43" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D43" s="13"/>
       <c r="J43" s="15"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D44" s="13"/>
       <c r="J44" s="15"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J46" s="15"/>
       <c r="K46" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="B47" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="J47" s="15"/>
       <c r="K47" t="s">
-        <v>59</v>
-      </c>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B48" s="17"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="8"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D49" s="8">
+        <v>22133684</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G49" s="9"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B50" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D50" s="8">
+        <v>22133633</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G50" s="9"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>97</v>
+      </c>
+      <c r="B51" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D51" s="8">
+        <v>22133631</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G51" s="9"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>97</v>
+      </c>
+      <c r="B52" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D52" s="8">
+        <v>22133632</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G52" s="9"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>97</v>
+      </c>
+      <c r="B53" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D53" s="8">
+        <v>22133627</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G53" s="9"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>97</v>
+      </c>
+      <c r="B54" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D54" s="8">
+        <v>22133678</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G54" s="9"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>97</v>
+      </c>
+      <c r="B55" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D55" s="8">
+        <v>22133639</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G55" s="9"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>97</v>
+      </c>
+      <c r="B56" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D56" s="8">
+        <v>22133623</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G56" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2354,36 +2558,36 @@
   <sheetData>
     <row r="1" spans="1:9" s="19" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="19" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B1" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="E1" s="19" t="s">
-        <v>74</v>
-      </c>
       <c r="F1" s="19" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G1" s="19" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H1" s="19" t="s">
         <v>31</v>
       </c>
       <c r="I1" s="19" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B2" s="18">
         <v>45819.666666666664</v>
@@ -2395,32 +2599,32 @@
         <v>22133650</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I2" s="19" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="68" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I3" s="19" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="68" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B4" s="18">
         <v>45828.711111111108</v>
@@ -2432,21 +2636,21 @@
         <v>22133637</v>
       </c>
       <c r="E4" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F4" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I4" s="19" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="136" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B5" s="18">
         <v>45831.260416666664</v>
@@ -2458,24 +2662,24 @@
         <v>22133651</v>
       </c>
       <c r="E5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="119" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B6" s="18">
         <v>45831.220833333333</v>
@@ -2487,24 +2691,24 @@
         <v>22133670</v>
       </c>
       <c r="E6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="H6" s="19" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I6" s="19" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B7" s="18">
         <v>45831.220138888886</v>
@@ -2516,19 +2720,19 @@
         <v>22133655</v>
       </c>
       <c r="E7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G7" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H7" s="19" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I7" s="19" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/data/2025/metadata/data_inventory.xlsx
+++ b/data/2025/metadata/data_inventory.xlsx
@@ -1,23 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/drotto/src/jiflr/data/2025/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D720A247-0A5F-1A41-9810-EC846048D1B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4FF41B2-5EF7-534F-9AE9-0D1E946BDCF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1180" yWindow="780" windowWidth="34820" windowHeight="22600" xr2:uid="{834A5152-98D4-1D4E-9988-BEC817907187}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="79">
   <si>
     <t>site_id</t>
   </si>
@@ -238,90 +236,6 @@
     <t>0m_unshielded</t>
   </si>
   <si>
-    <t>deployment time from photos</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>TKG4 2m</t>
-  </si>
-  <si>
-    <t>Site does not exist on caltopo</t>
-  </si>
-  <si>
-    <t>start time match .hobo file?</t>
-  </si>
-  <si>
-    <t>SN match .hobo file?</t>
-  </si>
-  <si>
-    <t>.hobo file serial number</t>
-  </si>
-  <si>
-    <t>.hobo file sensor name</t>
-  </si>
-  <si>
-    <t>C02 2m</t>
-  </si>
-  <si>
-    <t>.hobo file name</t>
-  </si>
-  <si>
-    <t>conclusion</t>
-  </si>
-  <si>
-    <t>Sensors with this label are mislabelled</t>
-  </si>
-  <si>
-    <t>TKG4 = A02</t>
-  </si>
-  <si>
-    <t>C01 2m</t>
-  </si>
-  <si>
-    <t>C01 (file does not exist)</t>
-  </si>
-  <si>
-    <t>This is correctly identified as G04</t>
-  </si>
-  <si>
-    <t>This is correctly identified as C02</t>
-  </si>
-  <si>
-    <t>This is correctly identified as G03</t>
-  </si>
-  <si>
-    <t>implied serial number from data_inventory sheet</t>
-  </si>
-  <si>
-    <t>A02 2m</t>
-  </si>
-  <si>
-    <t>G03 2m</t>
-  </si>
-  <si>
-    <t>G04 2m</t>
-  </si>
-  <si>
-    <t>G04 1m</t>
-  </si>
-  <si>
-    <t>C01 1m</t>
-  </si>
-  <si>
-    <t>"G03 100" is written on sensor and bag</t>
-  </si>
-  <si>
-    <t>This is correctly identified as G04 1m</t>
-  </si>
-  <si>
-    <t>"G03 200" is written on sensor and bag. Geotagged photo + personal memory agree that this site is at the bottom of the C10 hill</t>
-  </si>
-  <si>
-    <t>"A02 200" written on sensor and bag. By photo geotag, G04 -&gt; G03 order, and jeremy sensors at 1m, this is not the site at the bottom of the C10 hill</t>
-  </si>
-  <si>
     <t>on_ice_standard</t>
   </si>
   <si>
@@ -356,6 +270,9 @@
   </si>
   <si>
     <t>Poole Point</t>
+  </si>
+  <si>
+    <t>year</t>
   </si>
 </sst>
 </file>
@@ -443,7 +360,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -476,10 +393,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -821,8 +734,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{30214729-FAD1-AB4C-91D6-A2D7E03E2CE5}" name="Table2" displayName="Table2" ref="A1:K56" totalsRowShown="0" headerRowDxfId="11" tableBorderDxfId="10">
-  <autoFilter ref="A1:K56" xr:uid="{30214729-FAD1-AB4C-91D6-A2D7E03E2CE5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{30214729-FAD1-AB4C-91D6-A2D7E03E2CE5}" name="Table2" displayName="Table2" ref="B1:L56" totalsRowShown="0" headerRowDxfId="11" tableBorderDxfId="10">
+  <autoFilter ref="B1:L56" xr:uid="{30214729-FAD1-AB4C-91D6-A2D7E03E2CE5}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{D1314852-2294-C84C-828A-C37A76432716}" name="site_type"/>
     <tableColumn id="2" xr3:uid="{57B08370-AE15-194A-9E89-74600FFA2010}" name="site_id" dataDxfId="9"/>
@@ -1157,1380 +1070,1533 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{282355AC-F746-9947-AE42-F19047015063}">
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.83203125" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="14.1640625" customWidth="1"/>
-    <col min="7" max="7" width="21.1640625" customWidth="1"/>
-    <col min="8" max="8" width="15" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.33203125" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" style="1"/>
+    <col min="2" max="2" width="21.83203125" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="4" max="4" width="14.1640625" customWidth="1"/>
+    <col min="8" max="8" width="21.1640625" customWidth="1"/>
+    <col min="9" max="9" width="15" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B2" s="17" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2025</v>
+      </c>
+      <c r="B2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" s="8">
+      <c r="D2" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="8">
         <v>22133679</v>
       </c>
-      <c r="E2" s="5">
+      <c r="F2" s="5">
         <v>22133645</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G2" s="6">
+      <c r="G2" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="6">
         <v>45828.65625</v>
       </c>
-      <c r="H2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" s="5" t="s">
+      <c r="I2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="5"/>
+      <c r="K2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B3" s="17" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2025</v>
+      </c>
+      <c r="B3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="8">
+      <c r="D3" s="8">
         <v>22038780</v>
       </c>
-      <c r="D3" s="8">
+      <c r="E3" s="8">
         <v>22133650</v>
       </c>
-      <c r="E3" s="8">
+      <c r="F3" s="8">
         <v>22133682</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" s="9">
+      <c r="G3" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="9">
         <v>45819.701388888891</v>
       </c>
-      <c r="H3" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8" t="s">
-        <v>26</v>
-      </c>
+      <c r="I3" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="8"/>
       <c r="K3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B4" s="17" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2025</v>
+      </c>
+      <c r="B4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="5">
+      <c r="D4" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="5">
         <v>22133661</v>
       </c>
-      <c r="E4" s="5">
+      <c r="F4" s="5">
         <v>22133634</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="6">
+      <c r="G4" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="6">
         <v>45829.770833333336</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" s="5"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B5" s="17" t="s">
+      <c r="I4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="5"/>
+      <c r="K4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" s="5"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2025</v>
+      </c>
+      <c r="B5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="8">
+      <c r="D5" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="8">
         <v>22133638</v>
       </c>
-      <c r="E5" s="8">
+      <c r="F5" s="8">
         <v>22133641</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="9">
+      <c r="G5" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="9">
         <v>45829.75</v>
       </c>
-      <c r="H5" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" s="8"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>94</v>
-      </c>
-      <c r="B6" s="17" t="s">
+      <c r="I5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" s="8"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2025</v>
+      </c>
+      <c r="B6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="5">
+      <c r="D6" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="5">
         <v>22133644</v>
       </c>
-      <c r="E6" s="8">
+      <c r="F6" s="8">
         <v>22133664</v>
       </c>
-      <c r="F6" s="8">
+      <c r="G6" s="8">
         <v>10383220</v>
       </c>
-      <c r="G6" s="6">
+      <c r="H6" s="6">
         <v>45824.743055555555</v>
       </c>
-      <c r="H6" s="11"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="12" t="s">
+      <c r="I6" s="11"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="K6" s="8"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B7" s="17" t="s">
+      <c r="L6" s="8"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2025</v>
+      </c>
+      <c r="B7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="8">
+      <c r="D7" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="8">
         <v>22133672</v>
       </c>
-      <c r="E7" s="8">
+      <c r="F7" s="8">
         <v>22133660</v>
       </c>
-      <c r="F7" s="8">
+      <c r="G7" s="8">
         <v>10568651</v>
       </c>
-      <c r="G7" s="9">
+      <c r="H7" s="9">
         <v>45824.700694444444</v>
       </c>
-      <c r="H7" s="11"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K7" s="8"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>94</v>
-      </c>
-      <c r="B8" s="17" t="s">
+      <c r="I7" s="11"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="8"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2025</v>
+      </c>
+      <c r="B8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="D8" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="5">
         <v>22133667</v>
       </c>
-      <c r="E8" s="5">
+      <c r="F8" s="5">
         <v>22133640</v>
       </c>
-      <c r="F8" s="8">
+      <c r="G8" s="8">
         <v>10568642</v>
       </c>
-      <c r="G8" s="6">
+      <c r="H8" s="6">
         <v>45825.805555555555</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K8" s="8"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B9" s="17" t="s">
+      <c r="I8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="5"/>
+      <c r="K8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="8"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>2025</v>
+      </c>
+      <c r="B9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="8">
+      <c r="D9" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="8">
         <v>22133642</v>
       </c>
-      <c r="E9" s="8">
+      <c r="F9" s="8">
         <v>22133665</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="9">
+      <c r="G9" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" s="9">
         <v>45825.815972222219</v>
       </c>
-      <c r="H9" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K9" s="8"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>94</v>
-      </c>
-      <c r="B10" s="17" t="s">
+      <c r="I9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9" s="8"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2025</v>
+      </c>
+      <c r="B10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="D10" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="5">
         <v>22133683</v>
       </c>
-      <c r="E10" s="5">
+      <c r="F10" s="5">
         <v>22133656</v>
       </c>
-      <c r="F10" s="8">
+      <c r="G10" s="8">
         <v>9668113</v>
       </c>
-      <c r="G10" s="6">
+      <c r="H10" s="6">
         <v>45825.677083333336</v>
       </c>
-      <c r="H10" s="11"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K10" s="8"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>94</v>
-      </c>
-      <c r="B11" s="17" t="s">
+      <c r="I10" s="11"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L10" s="8"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2025</v>
+      </c>
+      <c r="B11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="8">
+      <c r="D11" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="8">
         <v>22133687</v>
       </c>
-      <c r="E11" s="8">
+      <c r="F11" s="8">
         <v>22133671</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" s="9">
+      <c r="G11" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="9">
         <v>45828.597222222219</v>
       </c>
-      <c r="H11" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K11" s="8"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>94</v>
-      </c>
-      <c r="B12" s="17" t="s">
+      <c r="I11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L11" s="8"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2025</v>
+      </c>
+      <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="D12" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="5">
         <v>22133680</v>
       </c>
-      <c r="E12" s="5">
+      <c r="F12" s="5">
         <v>22133663</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G12" s="6">
+      <c r="G12" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" s="6">
         <v>45820.713194444441</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="I12" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="5"/>
-      <c r="J12" s="8" t="s">
-        <v>26</v>
-      </c>
+      <c r="J12" s="5"/>
       <c r="K12" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L12" s="8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>94</v>
-      </c>
-      <c r="B13" s="17" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2025</v>
+      </c>
+      <c r="B13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="8">
+      <c r="D13" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="8">
         <v>22133635</v>
       </c>
-      <c r="E13" s="8">
+      <c r="F13" s="8">
         <v>22133624</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" s="9">
+      <c r="G13" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="9">
         <v>45820.697916666664</v>
       </c>
-      <c r="H13" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K13" s="8"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>94</v>
-      </c>
-      <c r="B14" s="17" t="s">
+      <c r="I13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13" s="8"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2025</v>
+      </c>
+      <c r="B14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="D14" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="5">
         <v>22133637</v>
       </c>
-      <c r="E14" s="5">
+      <c r="F14" s="5">
         <v>22133625</v>
       </c>
-      <c r="F14" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G14" s="6">
+      <c r="G14" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="6">
         <v>45828.715277777781</v>
       </c>
-      <c r="H14" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I14" s="5"/>
-      <c r="J14" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K14" s="8"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>94</v>
-      </c>
-      <c r="B15" s="17" t="s">
+      <c r="I14" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="5"/>
+      <c r="K14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" s="8"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2025</v>
+      </c>
+      <c r="B15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="8">
+      <c r="D15" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="8">
         <v>22133646</v>
       </c>
-      <c r="E15" s="8">
+      <c r="F15" s="8">
         <v>22133652</v>
       </c>
-      <c r="F15" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G15" s="9">
+      <c r="G15" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H15" s="9">
         <v>45829.722222222219</v>
       </c>
-      <c r="H15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K15" s="8"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>94</v>
-      </c>
-      <c r="B16" s="17" t="s">
+      <c r="I15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" s="8"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2025</v>
+      </c>
+      <c r="B16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="D16" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="5">
         <v>22133659</v>
       </c>
-      <c r="E16" s="5">
+      <c r="F16" s="5">
         <v>22133686</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" s="6">
+      <c r="G16" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H16" s="6">
         <v>45829.559027777781</v>
       </c>
-      <c r="H16" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I16" s="5"/>
-      <c r="J16" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K16" s="8"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>94</v>
-      </c>
-      <c r="B17" s="17" t="s">
+      <c r="I16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" s="5"/>
+      <c r="K16" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L16" s="8"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2025</v>
+      </c>
+      <c r="B17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="8">
+      <c r="D17" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="8">
         <v>22133630</v>
       </c>
-      <c r="E17" s="8">
+      <c r="F17" s="8">
         <v>22133636</v>
       </c>
-      <c r="F17" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G17" s="9">
+      <c r="G17" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H17" s="9">
         <v>45829.517361111109</v>
       </c>
-      <c r="H17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K17" s="8"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>94</v>
-      </c>
-      <c r="B18" s="17" t="s">
+      <c r="I17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" s="8"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>2025</v>
+      </c>
+      <c r="B18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="D18" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="5">
         <v>22133653</v>
       </c>
-      <c r="E18" s="5">
+      <c r="F18" s="5">
         <v>22133647</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G18" s="6">
+      <c r="G18" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H18" s="6">
         <v>45829.690972222219</v>
       </c>
-      <c r="H18" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I18" s="5"/>
-      <c r="J18" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K18" s="8"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>94</v>
-      </c>
-      <c r="B19" s="17" t="s">
+      <c r="I18" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J18" s="5"/>
+      <c r="K18" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L18" s="8"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>2025</v>
+      </c>
+      <c r="B19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" s="8">
+      <c r="D19" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="8">
         <v>22133674</v>
       </c>
-      <c r="E19" s="8">
+      <c r="F19" s="8">
         <v>22133626</v>
       </c>
-      <c r="F19" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G19" s="9">
+      <c r="G19" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H19" s="9">
         <v>45829.642361111109</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="I19" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K19" s="8"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>94</v>
-      </c>
-      <c r="B20" s="17" t="s">
+      <c r="J19" s="8"/>
+      <c r="K19" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L19" s="8"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>2025</v>
+      </c>
+      <c r="B20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="D20" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="5">
         <v>22133643</v>
       </c>
-      <c r="E20" s="5">
+      <c r="F20" s="5">
         <v>22133657</v>
       </c>
-      <c r="F20" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G20" s="6">
+      <c r="G20" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H20" s="6">
         <v>45829.614583333336</v>
       </c>
-      <c r="H20" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K20" s="8"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>94</v>
-      </c>
-      <c r="B21" s="17" t="s">
+      <c r="I20" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L20" s="8"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>2025</v>
+      </c>
+      <c r="B21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D21" s="8">
+      <c r="D21" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="8">
         <v>22133685</v>
       </c>
-      <c r="E21" s="8">
+      <c r="F21" s="8">
         <v>22133668</v>
       </c>
-      <c r="F21" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G21" s="9">
+      <c r="G21" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H21" s="9">
         <v>45830.489583333336</v>
       </c>
-      <c r="H21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K21" s="8"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>94</v>
-      </c>
-      <c r="B22" s="17" t="s">
+      <c r="I21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L21" s="8"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>2025</v>
+      </c>
+      <c r="B22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="D22" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="5">
         <v>22133669</v>
       </c>
-      <c r="E22" s="5">
+      <c r="F22" s="5">
         <v>22133629</v>
       </c>
-      <c r="F22" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G22" s="6">
+      <c r="G22" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H22" s="6">
         <v>45830.513888888891</v>
       </c>
-      <c r="H22" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K22" s="8"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B23" s="17" t="s">
+      <c r="I22" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L22" s="8"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>2025</v>
+      </c>
+      <c r="B23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D23" s="8">
+      <c r="D23" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="8">
         <v>22133673</v>
       </c>
-      <c r="E23" s="8">
+      <c r="F23" s="8">
         <v>22133676</v>
       </c>
-      <c r="F23" s="8">
+      <c r="G23" s="8">
         <v>10908287</v>
       </c>
-      <c r="G23" s="9">
+      <c r="H23" s="9">
         <v>45830.625</v>
       </c>
-      <c r="H23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K23" s="8"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>94</v>
-      </c>
-      <c r="B24" s="17" t="s">
+      <c r="I23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L23" s="8"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>2025</v>
+      </c>
+      <c r="B24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="D24" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="5">
         <v>22133648</v>
       </c>
-      <c r="E24" s="5">
+      <c r="F24" s="5">
         <v>22133675</v>
       </c>
-      <c r="F24" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G24" s="6">
+      <c r="G24" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H24" s="6">
         <v>45830.770833333336</v>
       </c>
-      <c r="H24" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K24" s="8"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>94</v>
-      </c>
-      <c r="B25" s="17" t="s">
+      <c r="I24" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L24" s="8"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>2025</v>
+      </c>
+      <c r="B25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D25" s="8">
+      <c r="D25" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" s="8">
         <v>22133628</v>
       </c>
-      <c r="E25" s="8">
+      <c r="F25" s="8">
         <v>22133666</v>
       </c>
-      <c r="F25" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G25" s="9">
+      <c r="G25" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H25" s="9">
         <v>45830.784722222219</v>
       </c>
-      <c r="H25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K25" s="8"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>94</v>
-      </c>
-      <c r="B26" s="17" t="s">
+      <c r="I25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L25" s="8"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>2025</v>
+      </c>
+      <c r="B26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D26" s="8">
+      <c r="D26" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" s="8">
         <v>22133651</v>
       </c>
-      <c r="E26" s="8">
+      <c r="F26" s="8">
         <v>10568620</v>
       </c>
-      <c r="F26" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G26" s="9">
+      <c r="G26" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H26" s="9">
         <v>45831.229166666664</v>
       </c>
-      <c r="H26" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8" t="s">
-        <v>26</v>
-      </c>
+      <c r="I26" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J26" s="8"/>
       <c r="K26" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L26" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>94</v>
-      </c>
-      <c r="B27" s="17" t="s">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>2025</v>
+      </c>
+      <c r="B27" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="D27" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F27" s="8">
         <v>10383462</v>
       </c>
-      <c r="F27" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G27" s="9">
+      <c r="G27" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H27" s="9">
         <v>45831.229166666664</v>
       </c>
-      <c r="H27" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K27" s="8"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>94</v>
-      </c>
-      <c r="B28" s="17" t="s">
+      <c r="I27" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L27" s="8"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>2025</v>
+      </c>
+      <c r="B28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D28" s="8">
+      <c r="D28" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="8">
         <v>22133670</v>
       </c>
-      <c r="E28" s="8">
+      <c r="F28" s="8">
         <v>22133655</v>
       </c>
-      <c r="F28" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G28" s="9">
+      <c r="G28" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H28" s="9">
         <v>45831.21875</v>
       </c>
-      <c r="H28" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8" t="s">
-        <v>26</v>
-      </c>
+      <c r="I28" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J28" s="8"/>
       <c r="K28" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L28" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B29" s="17"/>
-      <c r="C29" s="8"/>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C29" s="17"/>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="8"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B30" s="17"/>
-      <c r="C30" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="8"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C30" s="17"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="8"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>95</v>
-      </c>
-      <c r="B31" s="17" t="s">
+      <c r="G30" s="8"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="8"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>2025</v>
+      </c>
+      <c r="B31" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="C31" s="8">
+      <c r="D31" s="8">
         <v>22038781</v>
       </c>
-      <c r="D31" s="8">
+      <c r="E31" s="8">
         <v>22133681</v>
       </c>
-      <c r="E31" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="F31" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G31" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H31" s="9">
         <v>45830.739583333336</v>
       </c>
-      <c r="H31" s="11"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="11" t="s">
+      <c r="I31" s="11"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="K31" s="8"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>95</v>
-      </c>
-      <c r="B32" s="17" t="s">
+      <c r="L31" s="8"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>2025</v>
+      </c>
+      <c r="B32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C32" s="8">
+      <c r="D32" s="8">
         <v>22038779</v>
       </c>
-      <c r="D32" s="8">
+      <c r="E32" s="8">
         <v>22133658</v>
       </c>
-      <c r="E32" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="F32" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G32" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H32" s="9">
         <v>45827.774305555555</v>
       </c>
-      <c r="H32" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I32" s="8"/>
-      <c r="J32" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="K32" s="8"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>95</v>
-      </c>
-      <c r="B33" s="17" t="s">
+      <c r="I32" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J32" s="8"/>
+      <c r="K32" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L32" s="8"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>2025</v>
+      </c>
+      <c r="B33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="8">
+      <c r="D33" s="8">
         <v>22038776</v>
       </c>
-      <c r="D33" s="8">
+      <c r="E33" s="8">
         <v>22133654</v>
       </c>
-      <c r="E33" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="F33" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G33" s="9">
+      <c r="G33" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H33" s="9">
         <v>45827.6875</v>
       </c>
-      <c r="H33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I33" s="8"/>
-      <c r="J33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="K33" s="8"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>95</v>
-      </c>
-      <c r="B34" s="17" t="s">
+      <c r="I33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J33" s="8"/>
+      <c r="K33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L33" s="8"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>2025</v>
+      </c>
+      <c r="B34" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="C34" s="8">
+      <c r="D34" s="8">
         <v>22038777</v>
       </c>
-      <c r="D34" s="8">
+      <c r="E34" s="8">
         <v>22133649</v>
       </c>
-      <c r="E34" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="F34" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G34" s="9">
+      <c r="G34" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H34" s="9">
         <v>45825.791666666664</v>
       </c>
-      <c r="H34" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I34" s="8"/>
-      <c r="J34" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="K34" s="8"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>95</v>
-      </c>
-      <c r="B35" s="17" t="s">
+      <c r="I34" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J34" s="8"/>
+      <c r="K34" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L34" s="8"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>2025</v>
+      </c>
+      <c r="B35" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="8">
+      <c r="D35" s="8">
         <v>22038778</v>
       </c>
-      <c r="D35" s="8">
+      <c r="E35" s="8">
         <v>22133662</v>
       </c>
-      <c r="E35" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="F35" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G35" s="9">
+      <c r="G35" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H35" s="9">
         <v>45825.590277777781</v>
       </c>
-      <c r="H35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I35" s="8"/>
-      <c r="J35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="K35" s="8"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B36" s="17"/>
-      <c r="C36" s="8"/>
+      <c r="I35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J35" s="8"/>
+      <c r="K35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L35" s="8"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C36" s="17"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
       <c r="F36" s="8"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="8"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>96</v>
-      </c>
-      <c r="B37" s="17" t="s">
+      <c r="G36" s="8"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="8"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>2025</v>
+      </c>
+      <c r="B37" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C37" s="8"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="12"/>
       <c r="F37" s="8"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="8"/>
-      <c r="J37" s="16"/>
-      <c r="K37" s="8"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>96</v>
+      <c r="G37" s="8"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="8"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>2025</v>
       </c>
       <c r="B38" t="s">
+        <v>68</v>
+      </c>
+      <c r="C38" t="s">
         <v>45</v>
       </c>
-      <c r="D38" s="13"/>
-      <c r="J38" s="15"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>96</v>
+      <c r="E38" s="13"/>
+      <c r="K38" s="15"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>2025</v>
       </c>
       <c r="B39" t="s">
+        <v>68</v>
+      </c>
+      <c r="C39" t="s">
         <v>47</v>
       </c>
-      <c r="D39" s="13"/>
-      <c r="J39" s="15"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>96</v>
+      <c r="E39" s="13"/>
+      <c r="K39" s="15"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>2025</v>
       </c>
       <c r="B40" t="s">
+        <v>68</v>
+      </c>
+      <c r="C40" t="s">
         <v>46</v>
       </c>
-      <c r="D40" s="13"/>
-      <c r="J40" s="15"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>96</v>
-      </c>
-      <c r="B41" s="17" t="s">
+      <c r="E40" s="13"/>
+      <c r="K40" s="15"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>2025</v>
+      </c>
+      <c r="B41" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C41" s="8"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="14"/>
       <c r="F41" s="8"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="8"/>
-      <c r="J41" s="11"/>
-      <c r="K41" s="8"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>96</v>
+      <c r="G41" s="8"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="8"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>2025</v>
       </c>
       <c r="B42" t="s">
+        <v>68</v>
+      </c>
+      <c r="C42" t="s">
         <v>49</v>
       </c>
-      <c r="D42" s="13"/>
-      <c r="J42" s="15"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>96</v>
+      <c r="E42" s="13"/>
+      <c r="K42" s="15"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>2025</v>
       </c>
       <c r="B43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" t="s">
         <v>48</v>
       </c>
-      <c r="D43" s="13"/>
-      <c r="J43" s="15"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>96</v>
+      <c r="E43" s="13"/>
+      <c r="K43" s="15"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>2025</v>
       </c>
       <c r="B44" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" t="s">
         <v>50</v>
       </c>
-      <c r="D44" s="13"/>
-      <c r="J44" s="15"/>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>95</v>
+      <c r="E44" s="13"/>
+      <c r="K44" s="15"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>2025</v>
       </c>
       <c r="B46" t="s">
+        <v>67</v>
+      </c>
+      <c r="C46" t="s">
         <v>53</v>
       </c>
-      <c r="J46" s="15"/>
-      <c r="K46" t="s">
+      <c r="K46" s="15"/>
+      <c r="L46" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>95</v>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>2025</v>
       </c>
       <c r="B47" t="s">
+        <v>67</v>
+      </c>
+      <c r="C47" t="s">
         <v>52</v>
       </c>
-      <c r="J47" s="15"/>
-      <c r="K47" t="s">
+      <c r="K47" s="15"/>
+      <c r="L47" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B48" s="17"/>
-      <c r="C48" s="8"/>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C48" s="17"/>
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="8"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="8"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>97</v>
-      </c>
-      <c r="B49" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D49" s="8">
+      <c r="G48" s="8"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="8"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>2025</v>
+      </c>
+      <c r="B49" t="s">
+        <v>69</v>
+      </c>
+      <c r="C49" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E49" s="8">
         <v>22133684</v>
       </c>
-      <c r="E49" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="F49" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G49" s="9"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>97</v>
-      </c>
-      <c r="B50" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D50" s="8">
+      <c r="G49" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H49" s="9"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>2025</v>
+      </c>
+      <c r="B50" t="s">
+        <v>69</v>
+      </c>
+      <c r="C50" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E50" s="8">
         <v>22133633</v>
       </c>
-      <c r="E50" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="F50" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G50" s="9"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>97</v>
-      </c>
-      <c r="B51" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D51" s="8">
+      <c r="G50" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H50" s="9"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>2025</v>
+      </c>
+      <c r="B51" t="s">
+        <v>69</v>
+      </c>
+      <c r="C51" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E51" s="8">
         <v>22133631</v>
       </c>
-      <c r="E51" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="F51" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G51" s="9"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>97</v>
-      </c>
-      <c r="B52" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D52" s="8">
+      <c r="G51" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H51" s="9"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>2025</v>
+      </c>
+      <c r="B52" t="s">
+        <v>69</v>
+      </c>
+      <c r="C52" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E52" s="8">
         <v>22133632</v>
       </c>
-      <c r="E52" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="F52" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G52" s="9"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>97</v>
-      </c>
-      <c r="B53" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D53" s="8">
+      <c r="G52" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H52" s="9"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>2025</v>
+      </c>
+      <c r="B53" t="s">
+        <v>69</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E53" s="8">
         <v>22133627</v>
       </c>
-      <c r="E53" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="F53" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G53" s="9"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>97</v>
-      </c>
-      <c r="B54" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D54" s="8">
+      <c r="G53" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H53" s="9"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>2025</v>
+      </c>
+      <c r="B54" t="s">
+        <v>69</v>
+      </c>
+      <c r="C54" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E54" s="8">
         <v>22133678</v>
       </c>
-      <c r="E54" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="F54" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G54" s="9"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>97</v>
-      </c>
-      <c r="B55" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D55" s="8">
+      <c r="G54" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H54" s="9"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>2025</v>
+      </c>
+      <c r="B55" t="s">
+        <v>69</v>
+      </c>
+      <c r="C55" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E55" s="8">
         <v>22133639</v>
       </c>
-      <c r="E55" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="F55" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G55" s="9"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>97</v>
-      </c>
-      <c r="B56" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D56" s="8">
+      <c r="G55" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H55" s="9"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>2025</v>
+      </c>
+      <c r="B56" t="s">
+        <v>69</v>
+      </c>
+      <c r="C56" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E56" s="8">
         <v>22133623</v>
       </c>
-      <c r="E56" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="F56" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G56" s="9"/>
+      <c r="G56" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H56" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2539,204 +2605,4 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64892D2D-4B40-DA40-B7E4-D68118DD7E28}">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="15.1640625" customWidth="1"/>
-    <col min="2" max="2" width="30.1640625" customWidth="1"/>
-    <col min="3" max="3" width="31.6640625" customWidth="1"/>
-    <col min="4" max="4" width="21" customWidth="1"/>
-    <col min="5" max="5" width="16.1640625" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="8" max="8" width="19.1640625" style="19" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" style="19" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" s="19" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="B1" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="19" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B2" s="18">
-        <v>45819.666666666664</v>
-      </c>
-      <c r="C2">
-        <v>22133650</v>
-      </c>
-      <c r="D2">
-        <v>22133650</v>
-      </c>
-      <c r="E2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" t="s">
-        <v>68</v>
-      </c>
-      <c r="I2" s="19" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="51" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" s="19" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="34" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" s="18">
-        <v>45828.711111111108</v>
-      </c>
-      <c r="C4">
-        <v>22133637</v>
-      </c>
-      <c r="D4">
-        <v>22133637</v>
-      </c>
-      <c r="E4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G4" t="s">
-        <v>74</v>
-      </c>
-      <c r="I4" s="19" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="136" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B5" s="18">
-        <v>45831.260416666664</v>
-      </c>
-      <c r="C5">
-        <v>22133651</v>
-      </c>
-      <c r="D5">
-        <v>22133651</v>
-      </c>
-      <c r="E5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="I5" s="19" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="119" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="18">
-        <v>45831.220833333333</v>
-      </c>
-      <c r="C6">
-        <v>22133670</v>
-      </c>
-      <c r="D6">
-        <v>22133670</v>
-      </c>
-      <c r="E6" t="s">
-        <v>67</v>
-      </c>
-      <c r="F6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G6" t="s">
-        <v>79</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="I6" s="19" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="51" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B7" s="18">
-        <v>45831.220138888886</v>
-      </c>
-      <c r="C7">
-        <v>22133655</v>
-      </c>
-      <c r="D7">
-        <v>22133655</v>
-      </c>
-      <c r="E7" t="s">
-        <v>67</v>
-      </c>
-      <c r="F7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7" t="s">
-        <v>89</v>
-      </c>
-      <c r="H7" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="I7" s="19" t="s">
-        <v>91</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
 </file>